--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133582980</v>
+        <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örträsk, Vb</t>
+          <t>Lomnäset, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698226</v>
+        <v>698252</v>
       </c>
       <c r="R3" t="n">
-        <v>7119593</v>
+        <v>7119573</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133582980</t>
+          <t>https://artportalen.se/Sighting/137348519</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68676576</v>
+        <v>133582980</v>
       </c>
       <c r="B4" t="n">
-        <v>80298</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomnäset, Vb</t>
+          <t>Örträsk, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698514</v>
+        <v>698226</v>
       </c>
       <c r="R4" t="n">
-        <v>7119447</v>
+        <v>7119593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,17 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-06</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ID: Gudrun Norstedt</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,27 +974,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68676576</t>
+          <t>https://artportalen.se/Sighting/133582980</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67473989</v>
+        <v>68676576</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>80298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698524</v>
+        <v>698514</v>
       </c>
       <c r="R5" t="n">
-        <v>7119385</v>
+        <v>7119447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1064,11 @@
           <t>2017-09-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ID: Gudrun Norstedt</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1092,13 +1092,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473989</t>
+          <t>https://artportalen.se/Sighting/68676576</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67473993</v>
+        <v>67473989</v>
       </c>
       <c r="B6" t="n">
         <v>91909</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698632</v>
+        <v>698524</v>
       </c>
       <c r="R6" t="n">
-        <v>7119222</v>
+        <v>7119385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,16 +1194,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473993</t>
+          <t>https://artportalen.se/Sighting/67473989</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67473981</v>
+        <v>67473993</v>
       </c>
       <c r="B7" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698340</v>
+        <v>698632</v>
       </c>
       <c r="R7" t="n">
-        <v>7119646</v>
+        <v>7119222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,38 +1296,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473981</t>
+          <t>https://artportalen.se/Sighting/67473993</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67473979</v>
+        <v>67473981</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698301</v>
+        <v>698340</v>
       </c>
       <c r="R8" t="n">
-        <v>7119674</v>
+        <v>7119646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,13 +1398,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473979</t>
+          <t>https://artportalen.se/Sighting/67473981</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67473980</v>
+        <v>67473979</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698324</v>
+        <v>698301</v>
       </c>
       <c r="R9" t="n">
-        <v>7119687</v>
+        <v>7119674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,38 +1500,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473980</t>
+          <t>https://artportalen.se/Sighting/67473979</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67473998</v>
+        <v>67473980</v>
       </c>
       <c r="B10" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698608</v>
+        <v>698324</v>
       </c>
       <c r="R10" t="n">
-        <v>7119056</v>
+        <v>7119687</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,16 +1602,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473998</t>
+          <t>https://artportalen.se/Sighting/67473980</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>67473985</v>
+        <v>67473998</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698479</v>
+        <v>698608</v>
       </c>
       <c r="R11" t="n">
-        <v>7119513</v>
+        <v>7119056</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,56 +1704,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67473985</t>
+          <t>https://artportalen.se/Sighting/67473998</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>67474033</v>
+        <v>67473985</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lomnäset, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698347</v>
+        <v>698479</v>
       </c>
       <c r="R12" t="n">
-        <v>7119628</v>
+        <v>7119513</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,13 +1806,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67474033</t>
+          <t>https://artportalen.se/Sighting/67473985</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>67474034</v>
+        <v>67474033</v>
       </c>
       <c r="B13" t="n">
         <v>57953</v>
@@ -1848,7 +1843,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698359</v>
+        <v>698347</v>
       </c>
       <c r="R13" t="n">
-        <v>7119611</v>
+        <v>7119628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,51 +1913,56 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67474034</t>
+          <t>https://artportalen.se/Sighting/67474033</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>67473984</v>
+        <v>67474034</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lomnäset, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698371</v>
+        <v>698359</v>
       </c>
       <c r="R14" t="n">
-        <v>7119592</v>
+        <v>7119611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,7 +2020,211 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/67474034</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>67473984</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lomnäset, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698371</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7119592</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2017-09-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2017-09-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/67473984</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137348012</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lomnäset, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698450</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7119276</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Örträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137348012</t>
         </is>
       </c>
     </row>
@@ -2039,6 +2243,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/S 3393-2025 artfynd.xlsx
+++ b/artfynd/S 3393-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137348519</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>137348012</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
